--- a/Файлы/1 курс/2 семестр/Теоретическая информатика/Лабы/23.04.25 - Лаба №6/Дима/Лаб6.xlsx
+++ b/Файлы/1 курс/2 семестр/Теоретическая информатика/Лабы/23.04.25 - Лаба №6/Дима/Лаб6.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ibiat\Desktop\уник\ти\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luvidmi\Desktop\gitRep\Codespace\Файлы\1 курс\2 семестр\Теоретическая информатика\Лабы\23.04.25 - Лаба №6\Дима\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C49ACF-8A43-489E-B002-E616AE44E8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7485" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Моя семья" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,20 @@
     <sheet name="Следующий День Рождения" sheetId="5" r:id="rId5"/>
     <sheet name="ДЗ" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -338,7 +352,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -394,7 +408,6 @@
       <b/>
       <i/>
       <sz val="11"/>
-      <color theme="5" tint="-0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -516,7 +529,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -527,7 +540,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -576,8 +588,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -881,7 +908,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
@@ -898,15 +925,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -1053,7 +1080,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
@@ -1066,18 +1093,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="2" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="30" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1155,7 +1182,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
@@ -1170,26 +1197,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1209,9 +1236,9 @@
         <f>CHOOSE(C3,"Понедельник","Вторник","Среда","Четверг", "Пятница","Суббота","Воскресенье")</f>
         <v>Четверг</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="8">
         <f ca="1">TODAY()-B3</f>
-        <v>8538</v>
+        <v>8553</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1230,9 +1257,9 @@
         <f t="shared" ref="D4:D7" si="1">CHOOSE(C4,"Понедельник","Вторник","Среда","Четверг", "Пятница","Суббота","Воскресенье")</f>
         <v>Четверг</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="8">
         <f t="shared" ref="E4:E7" ca="1" si="2">TODAY()-B4</f>
-        <v>16357</v>
+        <v>16372</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1251,9 +1278,9 @@
         <f t="shared" si="1"/>
         <v>Суббота</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <f t="shared" ca="1" si="2"/>
-        <v>17552</v>
+        <v>17567</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1272,9 +1299,9 @@
         <f t="shared" si="1"/>
         <v>Пятница</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <f t="shared" ca="1" si="2"/>
-        <v>7256</v>
+        <v>7271</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1293,9 +1320,9 @@
         <f t="shared" si="1"/>
         <v>Суббота</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <f t="shared" ca="1" si="2"/>
-        <v>5288</v>
+        <v>5303</v>
       </c>
     </row>
   </sheetData>
@@ -1307,7 +1334,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF99CC"/>
   </sheetPr>
@@ -1315,173 +1342,173 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
     <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
     <col min="7" max="7" width="31.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+    </row>
+    <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="31"/>
+      <c r="B2" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="31" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="2" t="str">
+      <c r="F3" s="26" t="str">
         <f>CONCATENATE('Моя семья'!B3, " ",LEFT('Моя семья'!C3,1),".",LEFT('Моя семья'!D3,1),".")</f>
         <v>Николаева А.Д.</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="28" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="2" t="str">
+      <c r="F4" s="26" t="str">
         <f>CONCATENATE('Моя семья'!B4, " ",LEFT('Моя семья'!C4,1),".",LEFT('Моя семья'!D4,1),".")</f>
         <v>Николаева Е.А.</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="2" t="str">
+      <c r="F5" s="26" t="str">
         <f>CONCATENATE('Моя семья'!B5, " ",LEFT('Моя семья'!C5,1),".",LEFT('Моя семья'!D5,1),".")</f>
         <v>Николаев Д.М.</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="28" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="2" t="str">
+      <c r="F6" s="26" t="str">
         <f>CONCATENATE('Моя семья'!B6, " ",LEFT('Моя семья'!C6,1),".",LEFT('Моя семья'!D6,1),".")</f>
         <v>Николаев А.Д.</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="28" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="2" t="str">
+      <c r="F7" s="26" t="str">
         <f>CONCATENATE('Моя семья'!B7, " ",LEFT('Моя семья'!C7,1),".",LEFT('Моя семья'!D7,1),".")</f>
         <v>Николаева Е.Д.</v>
       </c>
-      <c r="G7" s="2"/>
+      <c r="G7" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1"/>
-    <hyperlink ref="G4" r:id="rId2"/>
-    <hyperlink ref="G5" r:id="rId3"/>
-    <hyperlink ref="G6" r:id="rId4"/>
+    <hyperlink ref="G3" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="G4" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="G5" r:id="rId3" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
+    <hyperlink ref="G6" r:id="rId4" xr:uid="{00000000-0004-0000-0300-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
@@ -1489,7 +1516,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor rgb="FFA9D08E"/>
   </sheetPr>
@@ -1505,30 +1532,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1554,7 +1581,7 @@
       </c>
       <c r="F3" s="2">
         <f ca="1">E3-TODAY()</f>
-        <v>228</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1579,7 +1606,7 @@
       </c>
       <c r="F4" s="2">
         <f t="shared" ref="F4:F7" ca="1" si="2">E4-TODAY()</f>
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1604,7 +1631,7 @@
       </c>
       <c r="F5" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>345</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1629,7 +1656,7 @@
       </c>
       <c r="F6" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>49</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1654,7 +1681,7 @@
       </c>
       <c r="F7" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>191</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -1666,11 +1693,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.28515625" bestFit="1" customWidth="1"/>
@@ -1683,729 +1710,731 @@
     <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="24.7109375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="8.85546875" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="11">
+    <row r="2" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="13" t="str">
+      <c r="E2" s="12" t="str">
         <f>CONCATENATE(B2," ",LEFT(C2,1),".",LEFT(D2,1),".")</f>
         <v>Булахова Е.М.</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="15">
         <v>101</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="10">
         <v>5</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="10">
         <v>5</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>5</v>
       </c>
-      <c r="J2" s="14">
+      <c r="J2" s="13">
         <f>AVERAGE(G2:I2)</f>
         <v>5</v>
       </c>
       <c r="S2">
         <v>101</v>
       </c>
-      <c r="T2" s="18" t="s">
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="10">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="12" t="str">
+        <f t="shared" ref="E3:E14" si="0">CONCATENATE(B3," ",LEFT(C3,1),".",LEFT(D3,1),".")</f>
+        <v>Галкина Д.С.</v>
+      </c>
+      <c r="F3" s="15">
+        <v>103</v>
+      </c>
+      <c r="G3" s="10">
+        <v>4</v>
+      </c>
+      <c r="H3" s="10">
+        <v>4</v>
+      </c>
+      <c r="I3" s="10">
+        <v>4</v>
+      </c>
+      <c r="J3" s="13">
+        <f t="shared" ref="J3:J14" si="1">AVERAGE(G3:I3)</f>
+        <v>4</v>
+      </c>
+      <c r="S3">
         <v>102</v>
       </c>
-      <c r="U2" s="15">
+    </row>
+    <row r="4" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="10">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Коваль А.М.</v>
+      </c>
+      <c r="F4" s="15">
+        <v>102</v>
+      </c>
+      <c r="G4" s="10">
+        <v>4</v>
+      </c>
+      <c r="H4" s="10">
+        <v>4</v>
+      </c>
+      <c r="I4" s="10">
+        <v>5</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" si="1"/>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="S4">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Матчин А.С.</v>
+      </c>
+      <c r="F5" s="15">
+        <v>102</v>
+      </c>
+      <c r="G5" s="10">
+        <v>2</v>
+      </c>
+      <c r="H5" s="10">
+        <v>5</v>
+      </c>
+      <c r="I5" s="10">
+        <v>3</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="S5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="10">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Морева П.М.</v>
+      </c>
+      <c r="F6" s="15">
+        <v>101</v>
+      </c>
+      <c r="G6" s="10">
+        <v>5</v>
+      </c>
+      <c r="H6" s="10">
+        <v>3</v>
+      </c>
+      <c r="I6" s="10">
+        <v>2</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="S6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="10">
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Новак О.А.</v>
+      </c>
+      <c r="F7" s="15">
+        <v>103</v>
+      </c>
+      <c r="G7" s="10">
+        <v>5</v>
+      </c>
+      <c r="H7" s="10">
+        <v>3</v>
+      </c>
+      <c r="I7" s="10">
+        <v>4</v>
+      </c>
+      <c r="J7" s="13">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Новиков Н.А.</v>
+      </c>
+      <c r="F8" s="15">
+        <v>102</v>
+      </c>
+      <c r="G8" s="10">
+        <v>4</v>
+      </c>
+      <c r="H8" s="10">
+        <v>4</v>
+      </c>
+      <c r="I8" s="10">
+        <v>4</v>
+      </c>
+      <c r="J8" s="13">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Пронькина Л.В.</v>
+      </c>
+      <c r="F9" s="15">
+        <v>101</v>
+      </c>
+      <c r="G9" s="10">
+        <v>5</v>
+      </c>
+      <c r="H9" s="10">
+        <v>2</v>
+      </c>
+      <c r="I9" s="10">
+        <v>2</v>
+      </c>
+      <c r="J9" s="13">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Солянник А.Г.</v>
+      </c>
+      <c r="F10" s="15">
+        <v>103</v>
+      </c>
+      <c r="G10" s="10">
+        <v>5</v>
+      </c>
+      <c r="H10" s="10">
+        <v>5</v>
+      </c>
+      <c r="I10" s="10">
+        <v>5</v>
+      </c>
+      <c r="J10" s="13">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Судьина Д.А.</v>
+      </c>
+      <c r="F11" s="15">
+        <v>101</v>
+      </c>
+      <c r="G11" s="10">
+        <v>3</v>
+      </c>
+      <c r="H11" s="10">
+        <v>5</v>
+      </c>
+      <c r="I11" s="10">
+        <v>4</v>
+      </c>
+      <c r="J11" s="13">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
+        <v>11</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Травкова А.В.</v>
+      </c>
+      <c r="F12" s="15">
+        <v>102</v>
+      </c>
+      <c r="G12" s="10">
+        <v>4</v>
+      </c>
+      <c r="H12" s="10">
+        <v>4</v>
+      </c>
+      <c r="I12" s="10">
+        <v>3</v>
+      </c>
+      <c r="J12" s="13">
+        <f t="shared" si="1"/>
+        <v>3.6666666666666665</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="10">
+        <v>12</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Уралова Н.И.</v>
+      </c>
+      <c r="F13" s="15">
+        <v>101</v>
+      </c>
+      <c r="G13" s="10">
+        <v>2</v>
+      </c>
+      <c r="H13" s="10">
+        <v>2</v>
+      </c>
+      <c r="I13" s="10">
+        <v>2</v>
+      </c>
+      <c r="J13" s="13">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="10">
+        <v>13</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Чубанова З.С.</v>
+      </c>
+      <c r="F14" s="15">
+        <v>102</v>
+      </c>
+      <c r="G14" s="10">
+        <v>3</v>
+      </c>
+      <c r="H14" s="10">
+        <v>3</v>
+      </c>
+      <c r="I14" s="10">
+        <v>4</v>
+      </c>
+      <c r="J14" s="13">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="F15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="16">
+        <f>AVERAGE(G2:G14)</f>
+        <v>3.9230769230769229</v>
+      </c>
+      <c r="H15" s="16">
+        <f t="shared" ref="H15:J15" si="2">AVERAGE(H2:H14)</f>
+        <v>3.7692307692307692</v>
+      </c>
+      <c r="I15" s="16">
+        <f t="shared" si="2"/>
+        <v>3.6153846153846154</v>
+      </c>
+      <c r="J15" s="16">
+        <f t="shared" si="2"/>
+        <v>3.7692307692307692</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B18" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="I18" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="24"/>
+      <c r="O18" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="P18" s="14">
         <f>COUNTIF(J2:J14,S5)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="13" t="str">
-        <f t="shared" ref="E3:E14" si="0">CONCATENATE(B3," ",LEFT(C3,1),".",LEFT(D3,1),".")</f>
-        <v>Галкина Д.С.</v>
-      </c>
-      <c r="F3" s="16">
-        <v>103</v>
-      </c>
-      <c r="G3" s="11">
-        <v>4</v>
-      </c>
-      <c r="H3" s="11">
-        <v>4</v>
-      </c>
-      <c r="I3" s="11">
-        <v>4</v>
-      </c>
-      <c r="J3" s="14">
-        <f t="shared" ref="J3:J14" si="1">AVERAGE(G3:I3)</f>
-        <v>4</v>
-      </c>
-      <c r="L3" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="25"/>
-      <c r="S3">
-        <v>102</v>
-      </c>
-      <c r="T3" s="18" t="s">
+    <row r="19" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="B19" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="L19" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="O19" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="U3" s="15">
+      <c r="P19" s="14">
         <f>COUNTIF(J2:J14,S8)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B20" s="17">
+        <v>101</v>
+      </c>
+      <c r="C20" s="16">
+        <f>(SUMIF($F$2:$F$14,$B20,G$2:G$14)/$F20)</f>
+        <v>4</v>
+      </c>
+      <c r="D20" s="16">
+        <f>(SUMIF($F$2:$F$14,$B20,H$2:H$14)/$F20)</f>
+        <v>3.4</v>
+      </c>
+      <c r="E20" s="16">
+        <f>(SUMIF($F$2:$F$14,$B20,I$2:I$14)/$F20)</f>
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Коваль А.М.</v>
-      </c>
-      <c r="F4" s="16">
+      <c r="F20" s="14">
+        <f>COUNTIF($F$2:$F$14,B20)</f>
+        <v>5</v>
+      </c>
+      <c r="G20" s="16">
+        <f>AVERAGE(C20:E20)</f>
+        <v>3.4666666666666668</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="J20" s="14">
+        <f>COUNTIF(G2:G14,$S5)</f>
+        <v>5</v>
+      </c>
+      <c r="K20" s="14">
+        <f>COUNTIF(H2:H14,$S5)</f>
+        <v>4</v>
+      </c>
+      <c r="L20" s="14">
+        <f>COUNTIF(I2:I14,$S5)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B21" s="17">
         <v>102</v>
       </c>
-      <c r="G4" s="11">
-        <v>4</v>
-      </c>
-      <c r="H4" s="11">
-        <v>4</v>
-      </c>
-      <c r="I4" s="11">
+      <c r="C21" s="16">
+        <f>(SUMIF($F$2:$F$14,$B21,G$2:G$14)/$F21)</f>
+        <v>3.4</v>
+      </c>
+      <c r="D21" s="16">
+        <f>(SUMIF($F$2:$F$14,$B21,H$2:H$14)/$F21)</f>
+        <v>4</v>
+      </c>
+      <c r="E21" s="16">
+        <f>(SUMIF($F$2:$F$14,$B21,I$2:I$14)/$F21)</f>
+        <v>3.8</v>
+      </c>
+      <c r="F21" s="14">
+        <f t="shared" ref="F21:F22" si="3">COUNTIF($F$2:$F$14,B21)</f>
         <v>5</v>
       </c>
-      <c r="J4" s="14">
-        <f t="shared" si="1"/>
+      <c r="G21" s="16">
+        <f t="shared" ref="G21:G22" si="4">AVERAGE(C21:E21)</f>
+        <v>3.7333333333333329</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="J21" s="14">
+        <f>COUNTIF(G3:G15,$S6)</f>
+        <v>4</v>
+      </c>
+      <c r="K21" s="14">
+        <f>COUNTIF(H3:H15,$S6)</f>
+        <v>4</v>
+      </c>
+      <c r="L21" s="14">
+        <f>COUNTIF(I3:I15,$S6)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B22" s="17">
+        <v>103</v>
+      </c>
+      <c r="C22" s="16">
+        <f>(SUMIF($F$2:$F$14,$B22,G$2:G$14)/$F22)</f>
+        <v>4.666666666666667</v>
+      </c>
+      <c r="D22" s="16">
+        <f>(SUMIF($F$2:$F$14,$B22,H$2:H$14)/$F22)</f>
+        <v>4</v>
+      </c>
+      <c r="E22" s="16">
+        <f>(SUMIF($F$2:$F$14,$B22,I$2:I$14)/$F22)</f>
         <v>4.333333333333333</v>
       </c>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="N4" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="O4" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="S4">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="11">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Матчин А.С.</v>
-      </c>
-      <c r="F5" s="16">
-        <v>102</v>
-      </c>
-      <c r="G5" s="11">
+      <c r="F22" s="14">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="G22" s="16">
+        <f t="shared" si="4"/>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="I22" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="J22" s="14">
+        <f>COUNTIF(G4:G16,$S7)</f>
         <v>2</v>
       </c>
-      <c r="H5" s="11">
-        <v>5</v>
-      </c>
-      <c r="I5" s="11">
+      <c r="K22" s="14">
+        <f>COUNTIF(H4:H16,$S7)</f>
         <v>3</v>
       </c>
-      <c r="J5" s="14">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="L5" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="M5" s="15">
-        <f t="shared" ref="M5:O8" si="2">COUNTIF(G2:G14,$S5)</f>
-        <v>5</v>
-      </c>
-      <c r="N5" s="15">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="O5" s="15">
-        <f t="shared" si="2"/>
+      <c r="L22" s="14">
+        <f>COUNTIF(I4:I16,$S7)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="I23" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="J23" s="14">
+        <f>COUNTIF(G5:G17,$S8)</f>
+        <v>2</v>
+      </c>
+      <c r="K23" s="14">
+        <f>COUNTIF(H5:H17,$S8)</f>
+        <v>2</v>
+      </c>
+      <c r="L23" s="14">
+        <f>COUNTIF(I5:I17,$S8)</f>
         <v>3</v>
-      </c>
-      <c r="S5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
-        <v>5</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Морева П.М.</v>
-      </c>
-      <c r="F6" s="16">
-        <v>101</v>
-      </c>
-      <c r="G6" s="11">
-        <v>5</v>
-      </c>
-      <c r="H6" s="11">
-        <v>3</v>
-      </c>
-      <c r="I6" s="11">
-        <v>2</v>
-      </c>
-      <c r="J6" s="14">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="L6" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="M6" s="15">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="N6" s="15">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="O6" s="15">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="S6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Новак О.А.</v>
-      </c>
-      <c r="F7" s="16">
-        <v>103</v>
-      </c>
-      <c r="G7" s="11">
-        <v>5</v>
-      </c>
-      <c r="H7" s="11">
-        <v>3</v>
-      </c>
-      <c r="I7" s="11">
-        <v>4</v>
-      </c>
-      <c r="J7" s="14">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L7" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="M7" s="15">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="N7" s="15">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="O7" s="15">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="S7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
-        <v>7</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Новиков Н.А.</v>
-      </c>
-      <c r="F8" s="16">
-        <v>102</v>
-      </c>
-      <c r="G8" s="11">
-        <v>4</v>
-      </c>
-      <c r="H8" s="11">
-        <v>4</v>
-      </c>
-      <c r="I8" s="11">
-        <v>4</v>
-      </c>
-      <c r="J8" s="14">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L8" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="M8" s="15">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="N8" s="15">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="O8" s="15">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="S8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
-        <v>8</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Пронькина Л.В.</v>
-      </c>
-      <c r="F9" s="16">
-        <v>101</v>
-      </c>
-      <c r="G9" s="11">
-        <v>5</v>
-      </c>
-      <c r="H9" s="11">
-        <v>2</v>
-      </c>
-      <c r="I9" s="11">
-        <v>2</v>
-      </c>
-      <c r="J9" s="14">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
-        <v>9</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Солянник А.Г.</v>
-      </c>
-      <c r="F10" s="16">
-        <v>103</v>
-      </c>
-      <c r="G10" s="11">
-        <v>5</v>
-      </c>
-      <c r="H10" s="11">
-        <v>5</v>
-      </c>
-      <c r="I10" s="11">
-        <v>5</v>
-      </c>
-      <c r="J10" s="14">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Судьина Д.А.</v>
-      </c>
-      <c r="F11" s="16">
-        <v>101</v>
-      </c>
-      <c r="G11" s="11">
-        <v>3</v>
-      </c>
-      <c r="H11" s="11">
-        <v>5</v>
-      </c>
-      <c r="I11" s="11">
-        <v>4</v>
-      </c>
-      <c r="J11" s="14">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
-        <v>11</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Травкова А.В.</v>
-      </c>
-      <c r="F12" s="16">
-        <v>102</v>
-      </c>
-      <c r="G12" s="11">
-        <v>4</v>
-      </c>
-      <c r="H12" s="11">
-        <v>4</v>
-      </c>
-      <c r="I12" s="11">
-        <v>3</v>
-      </c>
-      <c r="J12" s="14">
-        <f t="shared" si="1"/>
-        <v>3.6666666666666665</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
-        <v>12</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Уралова Н.И.</v>
-      </c>
-      <c r="F13" s="16">
-        <v>101</v>
-      </c>
-      <c r="G13" s="11">
-        <v>2</v>
-      </c>
-      <c r="H13" s="11">
-        <v>2</v>
-      </c>
-      <c r="I13" s="11">
-        <v>2</v>
-      </c>
-      <c r="J13" s="14">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
-        <v>13</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Чубанова З.С.</v>
-      </c>
-      <c r="F14" s="16">
-        <v>102</v>
-      </c>
-      <c r="G14" s="11">
-        <v>3</v>
-      </c>
-      <c r="H14" s="11">
-        <v>3</v>
-      </c>
-      <c r="I14" s="11">
-        <v>4</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="F15" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15" s="17">
-        <f>AVERAGE(G2:G14)</f>
-        <v>3.9230769230769229</v>
-      </c>
-      <c r="H15" s="17">
-        <f t="shared" ref="H15:J15" si="3">AVERAGE(H2:H14)</f>
-        <v>3.7692307692307692</v>
-      </c>
-      <c r="I15" s="17">
-        <f t="shared" si="3"/>
-        <v>3.6153846153846154</v>
-      </c>
-      <c r="J15" s="17">
-        <f t="shared" si="3"/>
-        <v>3.7692307692307692</v>
-      </c>
-    </row>
-    <row r="18" spans="11:16" x14ac:dyDescent="0.25">
-      <c r="K18" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="L18" s="26"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="26"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="26"/>
-    </row>
-    <row r="19" spans="11:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="K19" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="L19" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="M19" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="N19" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="O19" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="P19" s="20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="11:16" x14ac:dyDescent="0.25">
-      <c r="K20" s="18">
-        <v>101</v>
-      </c>
-      <c r="L20" s="17">
-        <f>(SUMIF($F$2:$F$14,$K20,G$2:G$14)/$O20)</f>
-        <v>4</v>
-      </c>
-      <c r="M20" s="17">
-        <f t="shared" ref="M20:N20" si="4">(SUMIF($F$2:$F$14,$K20,H$2:H$14)/$O20)</f>
-        <v>3.4</v>
-      </c>
-      <c r="N20" s="17">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="O20" s="15">
-        <f>COUNTIF($F$2:$F$14,K20)</f>
-        <v>5</v>
-      </c>
-      <c r="P20" s="17">
-        <f>AVERAGE(L20:N20)</f>
-        <v>3.4666666666666668</v>
-      </c>
-    </row>
-    <row r="21" spans="11:16" x14ac:dyDescent="0.25">
-      <c r="K21" s="18">
-        <v>102</v>
-      </c>
-      <c r="L21" s="17">
-        <f t="shared" ref="L21:L22" si="5">(SUMIF($F$2:$F$14,$K21,G$2:G$14)/$O21)</f>
-        <v>3.4</v>
-      </c>
-      <c r="M21" s="17">
-        <f t="shared" ref="M21:M22" si="6">(SUMIF($F$2:$F$14,$K21,H$2:H$14)/$O21)</f>
-        <v>4</v>
-      </c>
-      <c r="N21" s="17">
-        <f t="shared" ref="N21:N22" si="7">(SUMIF($F$2:$F$14,$K21,I$2:I$14)/$O21)</f>
-        <v>3.8</v>
-      </c>
-      <c r="O21" s="15">
-        <f t="shared" ref="O21:O22" si="8">COUNTIF($F$2:$F$14,K21)</f>
-        <v>5</v>
-      </c>
-      <c r="P21" s="17">
-        <f t="shared" ref="P21:P22" si="9">AVERAGE(L21:N21)</f>
-        <v>3.7333333333333329</v>
-      </c>
-    </row>
-    <row r="22" spans="11:16" x14ac:dyDescent="0.25">
-      <c r="K22" s="18">
-        <v>103</v>
-      </c>
-      <c r="L22" s="17">
-        <f t="shared" si="5"/>
-        <v>4.666666666666667</v>
-      </c>
-      <c r="M22" s="17">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="N22" s="17">
-        <f t="shared" si="7"/>
-        <v>4.333333333333333</v>
-      </c>
-      <c r="O22" s="15">
-        <f t="shared" si="8"/>
-        <v>3</v>
-      </c>
-      <c r="P22" s="17">
-        <f t="shared" si="9"/>
-        <v>4.333333333333333</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="L3:O3"/>
-    <mergeCell ref="K18:P18"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="B18:G18"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F14">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F14" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>$S$2:$S$4</formula1>
     </dataValidation>
   </dataValidations>
